--- a/Attendance/2nd year Foundation classes.xlsx
+++ b/Attendance/2nd year Foundation classes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRINCE SINGH\OneDrive\Documents\Desktop\CP\Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FD7BA4-203A-47AF-81C6-521E40DAF7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF9A811-4CBE-4CEE-9A9C-BF402A52684B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="59">
   <si>
     <t>S. no.</t>
   </si>
@@ -105,9 +105,6 @@
     <t>BHAVESH SANJAY PATIL</t>
   </si>
   <si>
-    <t>MECH</t>
-  </si>
-  <si>
     <t>Saner aarya sunil</t>
   </si>
   <si>
@@ -175,6 +172,36 @@
   </si>
   <si>
     <t>14 July AM</t>
+  </si>
+  <si>
+    <t>TINA VINOD SHIMPI</t>
+  </si>
+  <si>
+    <t>Patil Chaitanya Durgesh</t>
+  </si>
+  <si>
+    <t>Marathe Prathmesh</t>
+  </si>
+  <si>
+    <t>harshada tuakaram dhangar</t>
+  </si>
+  <si>
+    <t>aiml</t>
+  </si>
+  <si>
+    <t>mech</t>
+  </si>
+  <si>
+    <t>15 July AM</t>
+  </si>
+  <si>
+    <t>Ruchita sunil jadhav 251106027 DS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>16 Jul AM</t>
   </si>
 </sst>
 </file>
@@ -493,13 +520,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -513,10 +541,16 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -532,8 +566,14 @@
       <c r="F2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -549,8 +589,11 @@
       <c r="F3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -567,7 +610,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -580,8 +623,11 @@
       <c r="F5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -597,8 +643,11 @@
       <c r="F6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -614,8 +663,11 @@
       <c r="F7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -625,11 +677,20 @@
       <c r="D8" t="s">
         <v>19</v>
       </c>
+      <c r="E8">
+        <v>251101088</v>
+      </c>
       <c r="F8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -639,11 +700,17 @@
       <c r="D9" t="s">
         <v>21</v>
       </c>
+      <c r="E9">
+        <v>251106019</v>
+      </c>
       <c r="F9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -653,11 +720,17 @@
       <c r="D10" t="s">
         <v>19</v>
       </c>
+      <c r="E10">
+        <v>251101104</v>
+      </c>
       <c r="F10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -670,125 +743,161 @@
       <c r="F11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="E12" t="s">
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12">
+        <v>251103054</v>
+      </c>
+      <c r="F12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="F12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
         <v>30</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>31</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>32</v>
       </c>
-      <c r="E16" t="s">
-        <v>33</v>
-      </c>
       <c r="F16" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
         <v>34</v>
       </c>
-      <c r="D17" t="s">
-        <v>35</v>
-      </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
       </c>
+      <c r="E18">
+        <v>251102101</v>
+      </c>
       <c r="F18" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
       </c>
+      <c r="E19">
+        <v>251102042</v>
+      </c>
       <c r="F19" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="C20">
+        <v>251101084</v>
       </c>
       <c r="D20" t="s">
         <v>19</v>
@@ -796,82 +905,171 @@
       <c r="F20" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
         <v>40</v>
       </c>
-      <c r="D21" t="s">
-        <v>41</v>
-      </c>
       <c r="F21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" t="s">
         <v>47</v>
       </c>
-      <c r="D26" t="s">
-        <v>48</v>
-      </c>
       <c r="F26" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27">
+        <v>251101051</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="G27" t="s">
+        <v>6</v>
+      </c>
+      <c r="H27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28">
+        <v>251101058</v>
+      </c>
+      <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29">
+        <v>251101109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30">
+        <v>251107033</v>
+      </c>
+      <c r="E30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="H31" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Attendance/2nd year Foundation classes.xlsx
+++ b/Attendance/2nd year Foundation classes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRINCE SINGH\OneDrive\Documents\Desktop\CP\Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF9A811-4CBE-4CEE-9A9C-BF402A52684B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A8E810-468D-4AD6-B07B-E734E00E52A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
   <si>
     <t>S. no.</t>
   </si>
@@ -132,9 +132,6 @@
     <t>co1</t>
   </si>
   <si>
-    <t xml:space="preserve">     </t>
-  </si>
-  <si>
     <t>Borse dhruvang ajay</t>
   </si>
   <si>
@@ -202,6 +199,24 @@
   </si>
   <si>
     <t>16 Jul AM</t>
+  </si>
+  <si>
+    <t>17 Jul AM</t>
+  </si>
+  <si>
+    <t>18 Jul AM</t>
+  </si>
+  <si>
+    <t>ved rahul mahajan</t>
+  </si>
+  <si>
+    <t>pranav Bhaskar  Dhangar</t>
+  </si>
+  <si>
+    <t>Samkitt pravin jain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO3 </t>
   </si>
 </sst>
 </file>
@@ -520,14 +535,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="5" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -541,16 +557,22 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -572,8 +594,14 @@
       <c r="H2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -592,8 +620,14 @@
       <c r="H3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -609,8 +643,11 @@
       <c r="F4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -627,7 +664,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -646,8 +683,14 @@
       <c r="H6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -666,8 +709,14 @@
       <c r="H7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -689,8 +738,14 @@
       <c r="H8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -710,7 +765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -729,8 +784,14 @@
       <c r="G10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -747,7 +808,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -755,7 +816,7 @@
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12">
         <v>251103054</v>
@@ -769,44 +830,65 @@
       <c r="H12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="D13" t="s">
-        <v>35</v>
+      <c r="C13">
+        <v>251101121</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
+      <c r="C14">
+        <v>251101099</v>
+      </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
       </c>
+      <c r="C15">
+        <v>251101048</v>
+      </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15" t="s">
+        <v>6</v>
+      </c>
+      <c r="J15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -826,13 +908,13 @@
         <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -849,12 +931,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
@@ -869,12 +951,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
@@ -889,12 +971,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20">
         <v>251101084</v>
@@ -912,84 +994,84 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
         <v>39</v>
       </c>
-      <c r="D21" t="s">
-        <v>40</v>
-      </c>
       <c r="F21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="s">
         <v>46</v>
       </c>
-      <c r="D26" t="s">
-        <v>47</v>
-      </c>
       <c r="F26" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>251101051</v>
@@ -998,7 +1080,7 @@
         <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G27" t="s">
         <v>6</v>
@@ -1006,13 +1088,19 @@
       <c r="H27" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>251101058</v>
@@ -1023,13 +1111,16 @@
       <c r="G28" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>251101109</v>
@@ -1044,35 +1135,78 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D30">
         <v>251107033</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G30" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H31" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32">
+        <v>251101119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33">
+        <v>251101030</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34">
+        <v>251101131</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Attendance/2nd year Foundation classes.xlsx
+++ b/Attendance/2nd year Foundation classes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRINCE SINGH\OneDrive\Documents\Desktop\CP\Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A8E810-468D-4AD6-B07B-E734E00E52A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9CA519-2197-4AA0-A29E-84D0ED419B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="69">
   <si>
     <t>S. no.</t>
   </si>
@@ -217,6 +217,21 @@
   </si>
   <si>
     <t xml:space="preserve">CO3 </t>
+  </si>
+  <si>
+    <t>Manas Patil</t>
+  </si>
+  <si>
+    <t>20 Jul AM</t>
+  </si>
+  <si>
+    <t>Aaditya Patil</t>
+  </si>
+  <si>
+    <t>Pranav Patil</t>
+  </si>
+  <si>
+    <t>21 July AM</t>
   </si>
 </sst>
 </file>
@@ -535,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
@@ -543,7 +558,7 @@
     <col min="4" max="5" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -571,8 +586,14 @@
       <c r="J1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -601,7 +622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -627,7 +648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -647,7 +668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -664,7 +685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -690,7 +711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -716,7 +737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -744,8 +765,11 @@
       <c r="J8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -765,7 +789,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -790,8 +814,11 @@
       <c r="J10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -808,7 +835,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -834,7 +861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -848,7 +875,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -868,7 +895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -888,7 +915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -914,7 +941,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -931,7 +958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -951,7 +978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -971,7 +998,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -994,7 +1021,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1008,7 +1035,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1019,7 +1046,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1030,7 +1057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1041,7 +1068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1052,7 +1079,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1066,7 +1093,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1094,8 +1121,11 @@
       <c r="J27" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1114,8 +1144,11 @@
       <c r="I28" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1134,8 +1167,11 @@
       <c r="H29" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1152,7 +1188,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1163,7 +1199,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1177,7 +1213,7 @@
         <v>251101119</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1191,7 +1227,7 @@
         <v>251101030</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1203,6 +1239,45 @@
       </c>
       <c r="E34">
         <v>251101131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="K35" t="s">
+        <v>6</v>
+      </c>
+      <c r="L35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>66</v>
+      </c>
+      <c r="K36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="K37" t="s">
+        <v>6</v>
+      </c>
+      <c r="L37" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
